--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="152">
   <si>
     <t>sid</t>
   </si>
@@ -791,6 +791,12 @@
   </si>
   <si>
     <t>礼包码输入错误后需要等待的时间（单位：秒）</t>
+  </si>
+  <si>
+    <t>充值引导：点击充值引导图标，跳转客服链接</t>
+  </si>
+  <si>
+    <t>https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
   </si>
 </sst>
 </file>
@@ -1012,12 +1018,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1516,7 +1522,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1573,6 +1579,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1898,7 +1905,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2067,7 +2074,7 @@
       <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="15"/>
@@ -2084,7 +2091,7 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="40" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="12"/>
@@ -2101,7 +2108,7 @@
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="40" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="12"/>
@@ -2118,7 +2125,7 @@
       <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="40" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="12"/>
@@ -2135,7 +2142,7 @@
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="40" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="12"/>
@@ -3100,10 +3107,22 @@
         <v>10</v>
       </c>
     </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="8">
+        <v>125</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C81" s="38" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
     <hyperlink ref="C58" r:id="rId4" display="https://chat.kinghush.com/privacy.html"/>
+    <hyperlink ref="C81" r:id="rId5" display="https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -781,7 +781,7 @@
     <t>截图分享-在slot游戏中中奖达到多少倍触发截图分享</t>
   </si>
   <si>
-    <t>截图分享-在slot游戏中退出房间后重新进入房间获得X倍奖励是否触发截图分享（在当日分享次数足够时）</t>
+    <t>截图分享-在slot游戏中同一房间获得X倍奖励是否重复触发截图分享（在当日分享次数足够时）</t>
   </si>
   <si>
     <t>截图分享-在slot游戏中同一用户每日最多触发多少次截图分享</t>
@@ -1018,12 +1018,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1522,7 +1522,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1579,7 +1579,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2074,7 +2073,7 @@
       <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="38" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="15"/>
@@ -2091,7 +2090,7 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="39" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="12"/>
@@ -2108,7 +2107,7 @@
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="12"/>
@@ -2125,7 +2124,7 @@
       <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="39" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="12"/>
@@ -2142,7 +2141,7 @@
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="39" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="12"/>
@@ -2247,8 +2246,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="8">
-        <f>7*24*60*60</f>
-        <v>604800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3001,7 +2999,7 @@
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -3027,7 +3025,7 @@
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -3053,7 +3051,7 @@
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -3114,7 +3112,7 @@
       <c r="B81" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C81" s="38" t="s">
+      <c r="C81" s="33" t="s">
         <v>151</v>
       </c>
     </row>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
     <t>截图分享-在slot游戏中中奖达到多少倍触发截图分享</t>
   </si>
   <si>
-    <t>截图分享-在slot游戏中退出房间后重新进入房间获得X倍奖励是否触发截图分享（在当日分享次数足够时）</t>
+    <t>截图分享-在slot游戏中同一房间获得X倍奖励是否重复触发截图分享（在当日分享次数足够时）</t>
   </si>
   <si>
     <t>截图分享-在slot游戏中同一用户每日最多触发多少次截图分享</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -336,12 +336,57 @@
         </r>
       </text>
     </comment>
+    <comment ref="D82" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+间隔时间配置不能低于16s</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F82" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+TRUE表示开启
+FALSE表示关闭</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="158">
   <si>
     <t>sid</t>
   </si>
@@ -797,6 +842,24 @@
   </si>
   <si>
     <t>https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
+  </si>
+  <si>
+    <t>机器人跑马灯开关以及机器人跑马灯读取runninglight中数据间隔时间（毫秒）</t>
+  </si>
+  <si>
+    <t>免费旋转转盘抽奖结果控制（填转盘ID 第一次为1，第二次为2，填1_2）、后续获得比例万分比</t>
+  </si>
+  <si>
+    <t>7_2|7537</t>
+  </si>
+  <si>
+    <t>免费旋转分享转盘人数、流水（有效下注）、充值金额与人数要求（达到充值金额）</t>
+  </si>
+  <si>
+    <t>10|10000|1_1</t>
+  </si>
+  <si>
+    <t>免费旋转活动用户在每轮抽奖中需要达到的目标金额</t>
   </si>
 </sst>
 </file>
@@ -1522,7 +1585,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1578,6 +1641,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1904,7 +1970,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W81"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2073,7 +2139,7 @@
       <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="15"/>
@@ -2090,7 +2156,7 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="40" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="12"/>
@@ -2107,7 +2173,7 @@
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="40" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="12"/>
@@ -2124,7 +2190,7 @@
       <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="40" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="12"/>
@@ -2141,7 +2207,7 @@
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="40" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="12"/>
@@ -3105,7 +3171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:6">
       <c r="A81" s="8">
         <v>125</v>
       </c>
@@ -3114,6 +3180,53 @@
       </c>
       <c r="C81" s="33" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="8">
+        <v>126</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D82" s="8">
+        <v>20000</v>
+      </c>
+      <c r="F82" s="38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="8">
+        <v>127</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="8">
+        <v>128</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="8">
+        <v>129</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="8">
+        <v>1000000</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="159">
   <si>
     <t>sid</t>
   </si>
@@ -856,10 +856,13 @@
     <t>免费旋转分享转盘人数、流水（有效下注）、充值金额与人数要求（达到充值金额）</t>
   </si>
   <si>
-    <t>10|10000|1_1</t>
+    <t>10|10000|1|1</t>
   </si>
   <si>
     <t>免费旋转活动用户在每轮抽奖中需要达到的目标金额</t>
+  </si>
+  <si>
+    <t>免费旋转活动用户每轮抽奖持续的时间（单位：小时）</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +1973,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W85"/>
+  <dimension ref="A1:W86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3229,6 +3232,17 @@
         <v>1000000</v>
       </c>
     </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="8">
+        <v>130</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="8">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -381,12 +381,46 @@
         </r>
       </text>
     </comment>
+    <comment ref="C87" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+Administrator:
+游戏大类_有效的游戏ID范围|……
+1_-1|2_201000_200100|3_300400
+【游戏大类】
+1:slot类型游戏
+2:押注类游戏
+3:对战类游戏
+【有效的游戏ID】
+Warehouse表中的gameID
+-1:此类型的所有游戏
+100100：金矿大亨
+……
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="160">
   <si>
     <t>sid</t>
   </si>
@@ -853,7 +887,7 @@
     <t>7_2|7537</t>
   </si>
   <si>
-    <t>免费旋转分享转盘人数、流水（有效下注）、充值金额与人数要求（达到充值金额）</t>
+    <t>免费旋转分享转盘人数、游戏流水（游戏下注）、充值金额与人数要求（达到充值金额）</t>
   </si>
   <si>
     <t>10|10000|1|1</t>
@@ -863,6 +897,9 @@
   </si>
   <si>
     <t>免费旋转活动用户每轮抽奖持续的时间（单位：小时）</t>
+  </si>
+  <si>
+    <t>免费旋转活动被推广用户的流水游戏范围</t>
   </si>
 </sst>
 </file>
@@ -1973,7 +2010,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W86"/>
+  <dimension ref="A1:W87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3243,6 +3280,17 @@
         <v>72</v>
       </c>
     </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="8">
+        <v>131</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -851,7 +851,7 @@
     <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
   </si>
   <si>
-    <t>bindPhone()|1990000_3000|1_5_20_100|accountTotalRecharge(100)</t>
+    <t>bindPhone()|1970000_20000|1_5_20_100|accountTotalRecharge(0)</t>
   </si>
   <si>
     <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -851,7 +851,7 @@
     <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
   </si>
   <si>
-    <t>bindPhone()|1970000_20000|1_5_20_100|accountTotalRecharge(0)</t>
+    <t>bindPhone()|1970000_100000|1_5_20_100|accountTotalRecharge(0)</t>
   </si>
   <si>
     <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -881,16 +881,16 @@
     <t>机器人跑马灯开关以及机器人跑马灯读取runninglight中数据间隔时间（毫秒）</t>
   </si>
   <si>
-    <t>免费旋转转盘抽奖结果控制（填转盘ID 第一次为1，第二次为2，填1_2）、后续获得比例万分比</t>
-  </si>
-  <si>
-    <t>7_2|7537</t>
+    <t>免费旋转转盘抽奖结果控制（第一次抽奖的范围，万分比）、后续获得比例万分比</t>
+  </si>
+  <si>
+    <t>8000_9000|7537</t>
   </si>
   <si>
     <t>免费旋转分享转盘人数、游戏流水（游戏下注）、充值金额与人数要求（达到充值金额）</t>
   </si>
   <si>
-    <t>10|10000|1|1</t>
+    <t>6|179000|1|1</t>
   </si>
   <si>
     <t>免费旋转活动用户在每轮抽奖中需要达到的目标金额</t>
@@ -1121,12 +1121,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3266,7 +3266,7 @@
         <v>157</v>
       </c>
       <c r="D85" s="8">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="86" spans="1:6">

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="160">
   <si>
     <t>sid</t>
   </si>
@@ -772,7 +772,7 @@
     <t>活动-分享按钮：活动参与条件，不满足时分享失败|奖励道具ID_道具数量|每天账号领取次数_相同设备最多领取次数_注册IP地址领取次数_登录IP地址领取次数|领取奖励条件</t>
   </si>
   <si>
-    <t>bindPhone()|1990000_3000|1_5_20_100|accountTotalRecharge(100)</t>
+    <t>bindPhone()|1970000_100000|1_5_20_100|accountTotalRecharge(0)</t>
   </si>
   <si>
     <t>创建房间-房间时间上限，房间时长不能超过此值，单位：小时</t>
@@ -791,6 +791,36 @@
   </si>
   <si>
     <t>礼包码输入错误后需要等待的时间（单位：秒）</t>
+  </si>
+  <si>
+    <t>充值引导：点击充值引导图标，跳转客服链接</t>
+  </si>
+  <si>
+    <t>https://j5wxcf.7mmon3ss.com/chatwindow.aspx?siteId=65002831&amp;planId=c245fbe6-4ec5-46d6-8542-657f871cc0b3</t>
+  </si>
+  <si>
+    <t>机器人跑马灯开关以及机器人跑马灯读取runninglight中数据间隔时间（毫秒）</t>
+  </si>
+  <si>
+    <t>免费旋转转盘抽奖结果控制（第一次抽奖的范围，万分比）、后续获得比例万分比</t>
+  </si>
+  <si>
+    <t>8000_9000|7537</t>
+  </si>
+  <si>
+    <t>免费旋转分享转盘人数、游戏流水（游戏下注）、充值金额与人数要求（达到充值金额）</t>
+  </si>
+  <si>
+    <t>6|179000|1|1</t>
+  </si>
+  <si>
+    <t>免费旋转活动用户在每轮抽奖中需要达到的目标金额</t>
+  </si>
+  <si>
+    <t>免费旋转活动用户每轮抽奖持续的时间（单位：小时）</t>
+  </si>
+  <si>
+    <t>免费旋转活动被推广用户的流水游戏范围</t>
   </si>
 </sst>
 </file>
@@ -1898,7 +1928,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2994,7 +3024,7 @@
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -3020,7 +3050,7 @@
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -3046,7 +3076,7 @@
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -3100,6 +3130,86 @@
         <v>10</v>
       </c>
     </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="8">
+        <v>125</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="8">
+        <v>126</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D82" s="8">
+        <v>20000</v>
+      </c>
+      <c r="F82" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="8">
+        <v>127</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="8">
+        <v>128</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="8">
+        <v>129</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="8">
+        <v>130</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="8">
+        <v>131</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="161">
   <si>
     <t>sid</t>
   </si>
@@ -821,6 +821,9 @@
   </si>
   <si>
     <t>免费旋转活动被推广用户的流水游戏范围</t>
+  </si>
+  <si>
+    <t>奖励：广告收益倍数</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1931,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W87"/>
+  <dimension ref="A1:W88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3210,6 +3213,17 @@
         <v>131</v>
       </c>
     </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="8">
+        <v>135</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D88" s="8">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="164">
   <si>
     <t>sid</t>
   </si>
@@ -823,7 +823,16 @@
     <t>免费旋转活动被推广用户的流水游戏范围</t>
   </si>
   <si>
-    <t>奖励：广告收益倍数</t>
+    <t>广告：奖励收益倍数(必随机一个倍数)</t>
+  </si>
+  <si>
+    <t>1.5_2000|2_2000|3_3000</t>
+  </si>
+  <si>
+    <t>广告：建筑每次升级看广告次数</t>
+  </si>
+  <si>
+    <t>游客在赌场中设备的交互时间（秒）</t>
   </si>
 </sst>
 </file>
@@ -1931,7 +1940,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3220,8 +3229,30 @@
       <c r="B88" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D88" s="8">
-        <v>2</v>
+      <c r="C88" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="8">
+        <v>136</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D89" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="8">
+        <v>200</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D90" s="8">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="169">
   <si>
     <t>sid</t>
   </si>
@@ -833,6 +833,21 @@
   </si>
   <si>
     <t>游客在赌场中设备的交互时间（秒）</t>
+  </si>
+  <si>
+    <t>赌场信息：游戏总数量 (赌场ID_游戏ID|赌场ID_游戏ID)</t>
+  </si>
+  <si>
+    <t>1_100100_100200_100300</t>
+  </si>
+  <si>
+    <t>赌场信息：雇员总数量 (赌场ID_雇员总数量|赌场ID_雇员总数量)</t>
+  </si>
+  <si>
+    <t>赌场信息：容纳游客总数 (赌场ID_游客总数量|赌场ID_游客总数量)</t>
+  </si>
+  <si>
+    <t>1_200</t>
   </si>
 </sst>
 </file>
@@ -1940,7 +1955,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W90"/>
+  <dimension ref="A1:W93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3255,6 +3270,39 @@
         <v>5</v>
       </c>
     </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="8">
+        <v>211</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="8">
+        <v>212</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="8">
+        <v>213</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -336,12 +336,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="B90" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置为空或0，表示不限次数</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="170">
   <si>
     <t>sid</t>
   </si>
@@ -827,6 +849,9 @@
   </si>
   <si>
     <t>1.5_2000|2_2000|3_3000</t>
+  </si>
+  <si>
+    <t>广告：看一次广告清除的时间(分)</t>
   </si>
   <si>
     <t>广告：建筑每次升级看广告次数</t>
@@ -1955,7 +1980,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W93"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3256,51 +3281,62 @@
         <v>162</v>
       </c>
       <c r="D89" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="8">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>163</v>
       </c>
       <c r="D90" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="8">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>165</v>
+      <c r="D91" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B92" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="8">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>167</v>
       </c>
       <c r="C93" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="8">
+        <v>213</v>
+      </c>
+      <c r="B94" s="8" t="s">
         <v>168</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="171">
   <si>
     <t>sid</t>
   </si>
@@ -873,6 +873,9 @@
   </si>
   <si>
     <t>1_200</t>
+  </si>
+  <si>
+    <t>建筑：建造加速道具ID</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +1983,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3339,6 +3342,17 @@
         <v>169</v>
       </c>
     </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="8">
+        <v>220</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D95" s="8">
+        <v>1024007</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="196">
   <si>
     <t>sid</t>
   </si>
@@ -876,6 +876,81 @@
   </si>
   <si>
     <t>建筑：建造加速道具ID</t>
+  </si>
+  <si>
+    <t>联盟：联盟的创建条件：需要用户达到的等级数</t>
+  </si>
+  <si>
+    <t>联盟：创建联盟需要消耗的道具与数量</t>
+  </si>
+  <si>
+    <t>1980000_200</t>
+  </si>
+  <si>
+    <t>联盟：联盟任务列表中任务条数上限</t>
+  </si>
+  <si>
+    <t>联盟：用户每日完成联盟任务的次数上限</t>
+  </si>
+  <si>
+    <t>联盟：用户建筑加速每日被帮助次数上限</t>
+  </si>
+  <si>
+    <t>联盟：用户每日给盟友可提供的加速次数上限</t>
+  </si>
+  <si>
+    <t>联盟：用户的建筑被帮助加速一次可减少的时间（分钟）</t>
+  </si>
+  <si>
+    <t>联盟：用户帮助求助者一次可获得的贡献值数量</t>
+  </si>
+  <si>
+    <t>联盟：用户每日捐献的次数</t>
+  </si>
+  <si>
+    <t>联盟：用户用于捐献的物品和数量</t>
+  </si>
+  <si>
+    <t>1980000_50</t>
+  </si>
+  <si>
+    <t>联盟：用户捐献后获得的贡献值奖励数量</t>
+  </si>
+  <si>
+    <t>拜访：点赞一次可以获得的人气值（被点赞的玩家）</t>
+  </si>
+  <si>
+    <t>拜访：留言一条可以获得的人气值（被留言的玩家）</t>
+  </si>
+  <si>
+    <t>拜访：试玩一次slot游戏可以获得人气值（房主）</t>
+  </si>
+  <si>
+    <t>拜访：每天可以获得的人气值上限</t>
+  </si>
+  <si>
+    <t>拜访：每日可以试玩slot的次数</t>
+  </si>
+  <si>
+    <t>拜访：用户在试玩slot游戏中，获胜时被抽取的比例（百分比）</t>
+  </si>
+  <si>
+    <t>多人任务：用户每日最多领取任务次数</t>
+  </si>
+  <si>
+    <t>多人任务：任务列表中每日从任务池中随机抽取任务的个数</t>
+  </si>
+  <si>
+    <t>多人任务：刷新任务列表所需要的道具及数量</t>
+  </si>
+  <si>
+    <t>好友聊天：每日赠送礼物详情</t>
+  </si>
+  <si>
+    <t>1980000_10_1_50</t>
+  </si>
+  <si>
+    <t>物品id_物品数量_赠送次数上限_赠送人数上限</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1657,6 +1732,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1983,7 +2061,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W95"/>
+  <dimension ref="A1:W116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2152,7 +2230,7 @@
       <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="15"/>
@@ -2169,7 +2247,7 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="40" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="12"/>
@@ -2186,7 +2264,7 @@
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="40" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="12"/>
@@ -2203,7 +2281,7 @@
       <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="40" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="12"/>
@@ -2220,7 +2298,7 @@
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="40" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="12"/>
@@ -3353,6 +3431,248 @@
         <v>1024007</v>
       </c>
     </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="8">
+        <v>221</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D96" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="8">
+        <v>222</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C97" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="8">
+        <v>223</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C98" s="38"/>
+      <c r="D98" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="8">
+        <v>224</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C99" s="38"/>
+      <c r="D99" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="8">
+        <v>225</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" s="38"/>
+      <c r="D100" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="8">
+        <v>226</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C101" s="38"/>
+      <c r="D101" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="8">
+        <v>227</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C102" s="38"/>
+      <c r="D102" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="8">
+        <v>228</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C103" s="38"/>
+      <c r="D103" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="8">
+        <v>229</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C104" s="38"/>
+      <c r="D104" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="8">
+        <v>230</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C105" s="38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="8">
+        <v>231</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C106" s="38"/>
+      <c r="D106" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="8">
+        <v>232</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D107" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="8">
+        <v>233</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D108" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="8">
+        <v>234</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D109" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="8">
+        <v>235</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D110" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="8">
+        <v>236</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D111" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="8">
+        <v>237</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D112" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="8">
+        <v>238</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D113" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="8">
+        <v>239</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D114" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="8">
+        <v>240</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C115" s="38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="8">
+        <v>241</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="198">
   <si>
     <t>sid</t>
   </si>
@@ -911,39 +911,42 @@
     <t>联盟：用户用于捐献的物品和数量</t>
   </si>
   <si>
+    <t>1980000_0,20,30,40,50</t>
+  </si>
+  <si>
+    <t>联盟：用户捐献后获得的贡献值奖励数量</t>
+  </si>
+  <si>
+    <t>拜访：点赞一次可以获得的人气值（被点赞的玩家）</t>
+  </si>
+  <si>
+    <t>拜访：留言一条可以获得的人气值（被留言的玩家）</t>
+  </si>
+  <si>
+    <t>拜访：试玩一次slot游戏可以获得人气值（房主）</t>
+  </si>
+  <si>
+    <t>拜访：每天可以获得的人气值上限</t>
+  </si>
+  <si>
+    <t>拜访：每日可以试玩slot的次数</t>
+  </si>
+  <si>
+    <t>拜访：用户在试玩slot游戏中，获胜时被抽取的比例（百分比）</t>
+  </si>
+  <si>
+    <t>多人任务：用户每日最多领取任务次数</t>
+  </si>
+  <si>
+    <t>多人任务：任务列表中每日从任务池中随机抽取任务的个数</t>
+  </si>
+  <si>
+    <t>多人任务：刷新任务列表所需要的道具及数量</t>
+  </si>
+  <si>
     <t>1980000_50</t>
   </si>
   <si>
-    <t>联盟：用户捐献后获得的贡献值奖励数量</t>
-  </si>
-  <si>
-    <t>拜访：点赞一次可以获得的人气值（被点赞的玩家）</t>
-  </si>
-  <si>
-    <t>拜访：留言一条可以获得的人气值（被留言的玩家）</t>
-  </si>
-  <si>
-    <t>拜访：试玩一次slot游戏可以获得人气值（房主）</t>
-  </si>
-  <si>
-    <t>拜访：每天可以获得的人气值上限</t>
-  </si>
-  <si>
-    <t>拜访：每日可以试玩slot的次数</t>
-  </si>
-  <si>
-    <t>拜访：用户在试玩slot游戏中，获胜时被抽取的比例（百分比）</t>
-  </si>
-  <si>
-    <t>多人任务：用户每日最多领取任务次数</t>
-  </si>
-  <si>
-    <t>多人任务：任务列表中每日从任务池中随机抽取任务的个数</t>
-  </si>
-  <si>
-    <t>多人任务：刷新任务列表所需要的道具及数量</t>
-  </si>
-  <si>
     <t>好友聊天：每日赠送礼物详情</t>
   </si>
   <si>
@@ -951,6 +954,9 @@
   </si>
   <si>
     <t>物品id_物品数量_赠送次数上限_赠送人数上限</t>
+  </si>
+  <si>
+    <t>联盟：用户捐献后获得的声誉值奖励数量</t>
   </si>
 </sst>
 </file>
@@ -1676,7 +1682,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1734,6 +1740,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -2061,7 +2070,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W116"/>
+  <dimension ref="A1:W117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2230,7 +2239,7 @@
       <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="40" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="15"/>
@@ -2247,7 +2256,7 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="41" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="12"/>
@@ -2264,7 +2273,7 @@
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="41" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="12"/>
@@ -2281,7 +2290,7 @@
       <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="41" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="12"/>
@@ -2298,7 +2307,7 @@
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="41" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="12"/>
@@ -3544,7 +3553,7 @@
       <c r="B105" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C105" s="38" t="s">
+      <c r="C105" s="39" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3656,7 +3665,7 @@
         <v>192</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3664,13 +3673,24 @@
         <v>241</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="8">
+        <v>242</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D117" s="8">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="201">
   <si>
     <t>sid</t>
   </si>
@@ -963,6 +963,9 @@
   </si>
   <si>
     <t>1024017_3_1</t>
+  </si>
+  <si>
+    <t>角色信息：勋章展示数量上限</t>
   </si>
 </sst>
 </file>
@@ -1184,12 +1187,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2076,7 +2079,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W118"/>
+  <dimension ref="A1:W119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3710,6 +3713,17 @@
         <v>199</v>
       </c>
     </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="8">
+        <v>251</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D119" s="8">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="206">
   <si>
     <t>sid</t>
   </si>
@@ -963,6 +963,21 @@
   </si>
   <si>
     <t>1024017_3_1</t>
+  </si>
+  <si>
+    <t>拜访：访客每日点赞次数上限</t>
+  </si>
+  <si>
+    <t>拜访：访客每日留言次数上限</t>
+  </si>
+  <si>
+    <t>拜访：留言功能解锁的累计充值门槛</t>
+  </si>
+  <si>
+    <t>拜访：留言最大字符数（按 Unicode code point 计）</t>
+  </si>
+  <si>
+    <t>拜访：房主每日试玩抽成金币上限</t>
   </si>
   <si>
     <t>角色信息：勋章展示数量上限</t>
@@ -2079,7 +2094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W119"/>
+  <dimension ref="A1:W124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3715,12 +3730,67 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="8">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B119" s="8" t="s">
         <v>200</v>
       </c>
       <c r="D119" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="8">
+        <v>245</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D120" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="8">
+        <v>246</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D121" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="8">
+        <v>247</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D122" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="8">
+        <v>248</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D123" s="8">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="8">
+        <v>251</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D124" s="8">
         <v>10</v>
       </c>
     </row>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="207">
   <si>
     <t>sid</t>
   </si>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>拜访：房主每日试玩抽成金币上限</t>
+  </si>
+  <si>
+    <t>联盟：用户每日在建筑上进行分享的次数上限（减少建筑CD）</t>
   </si>
   <si>
     <t>角色信息：勋章展示数量上限</t>
@@ -1202,12 +1205,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2094,7 +2097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W124"/>
+  <dimension ref="A1:W125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3785,12 +3788,23 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="8">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B124" s="8" t="s">
         <v>205</v>
       </c>
       <c r="D124" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="8">
+        <v>251</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D125" s="8">
         <v>10</v>
       </c>
     </row>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="209">
   <si>
     <t>sid</t>
   </si>
@@ -719,7 +719,7 @@
     <t>隐私政策链接</t>
   </si>
   <si>
-    <t>https://chat.kinghush.com/privacy.html</t>
+    <t>https://lls.cdjjgkj.cn/privacy-policy.html</t>
   </si>
   <si>
     <t>推广分享：分享1人得固定奖励</t>
@@ -984,6 +984,12 @@
   </si>
   <si>
     <t>角色信息：勋章展示数量上限</t>
+  </si>
+  <si>
+    <t>用户协议：链接配置</t>
+  </si>
+  <si>
+    <t>https://lls.cdjjgkj.cn/terms-of-service.html</t>
   </si>
 </sst>
 </file>
@@ -1205,12 +1211,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2097,7 +2103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W125"/>
+  <dimension ref="A1:W126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3808,10 +3814,21 @@
         <v>10</v>
       </c>
     </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="8">
+        <v>261</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
-    <hyperlink ref="C58" r:id="rId4" display="https://chat.kinghush.com/privacy.html"/>
+    <hyperlink ref="C58" r:id="rId4" display="https://lls.cdjjgkj.cn/privacy-policy.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="212">
   <si>
     <t>sid</t>
   </si>
@@ -990,6 +990,15 @@
   </si>
   <si>
     <t>https://lls.cdjjgkj.cn/terms-of-service.html</t>
+  </si>
+  <si>
+    <t>斗仙牌复活游戏所需钻石金额以及复活后赠送金币金额</t>
+  </si>
+  <si>
+    <t>300800,1980000_20|1990000_10000</t>
+  </si>
+  <si>
+    <t>游戏id,复活所需要的钻石_数量|赠送的金币_数量</t>
   </si>
 </sst>
 </file>
@@ -2103,7 +2112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W126"/>
+  <dimension ref="A1:W127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3825,6 +3834,20 @@
         <v>208</v>
       </c>
     </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="8">
+        <v>270</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="164">
   <si>
     <t>sid</t>
   </si>
@@ -824,6 +824,15 @@
   </si>
   <si>
     <t>奖励：广告收益倍数</t>
+  </si>
+  <si>
+    <t>斗仙牌复活游戏所需钻石金额以及复活后赠送金币金额</t>
+  </si>
+  <si>
+    <t>300800,1980000_20|1990000_10000</t>
+  </si>
+  <si>
+    <t>游戏id,复活所需要的钻石_数量|赠送的金币_数量</t>
   </si>
 </sst>
 </file>
@@ -1549,7 +1558,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1558,6 +1567,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1931,378 +1941,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="8"/>
-    <col min="2" max="2" width="134.125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="36.5" style="8" customWidth="1"/>
-    <col min="4" max="4" width="28.375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="8" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="23.375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="8"/>
-    <col min="9" max="10" width="14.125" style="8"/>
-    <col min="11" max="11" width="9" style="8"/>
-    <col min="12" max="12" width="12.875" style="8"/>
-    <col min="13" max="13" width="9" style="8"/>
-    <col min="14" max="17" width="10.375" style="8"/>
-    <col min="18" max="18" width="9.25" style="8"/>
-    <col min="19" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="134.125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="36.5" style="9" customWidth="1"/>
+    <col min="4" max="4" width="28.375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="9" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="23.375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="9"/>
+    <col min="9" max="10" width="14.125" style="9"/>
+    <col min="11" max="11" width="9" style="9"/>
+    <col min="12" max="12" width="12.875" style="9"/>
+    <col min="13" max="13" width="9" style="9"/>
+    <col min="14" max="17" width="10.375" style="9"/>
+    <col min="18" max="18" width="9.25" style="9"/>
+    <col min="19" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="13"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>999</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <v>10000</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <v>10000</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="s">
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="8">
+      <c r="A8" s="9">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <v>100</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <v>4</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="8">
+      <c r="A10" s="9">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="8" t="s">
+      <c r="D10" s="16"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="8">
+      <c r="A11" s="9">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="8" t="s">
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="8">
+      <c r="A12" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="8" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="8">
+      <c r="A13" s="9">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="8" t="s">
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="8">
+      <c r="A14" s="9">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="8" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="8">
+      <c r="A15" s="9">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>2*3*5*3</f>
         <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="8">
+      <c r="A16" s="9">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9">
         <v>3333</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="8">
+      <c r="A17" s="9">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="8">
+      <c r="A18" s="9">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="8">
+      <c r="A19" s="9">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="8">
+      <c r="A20" s="9">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="9">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="8">
+      <c r="A21" s="9">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="8">
+      <c r="A22" s="9">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="9">
         <f>7*24*60*60</f>
         <v>604800</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="8">
+      <c r="A23" s="9">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="9">
         <f>60*24*30</f>
         <v>43200</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="8">
+      <c r="A24" s="9">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="9">
         <v>10</v>
       </c>
     </row>
@@ -2313,7 +2323,7 @@
       <c r="B25" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2368,58 +2378,58 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="8">
+      <c r="A30" s="9">
         <v>26</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="8">
+      <c r="C30" s="19"/>
+      <c r="D30" s="9">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="8">
+      <c r="A31" s="9">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="9">
         <v>10000</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="8">
+      <c r="A32" s="9">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="8">
+      <c r="A33" s="9">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="9">
         <v>10</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" spans="1:23">
-      <c r="A34" s="19">
+      <c r="A34" s="20">
         <v>30</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="20" t="s">
         <v>67</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2427,19 +2437,19 @@
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="1:23">
-      <c r="A35" s="19">
+      <c r="A35" s="20">
         <v>31</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <v>372460972.440945</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="21">
         <v>8692.20472440945</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -2460,10 +2470,10 @@
       </c>
     </row>
     <row r="36" spans="1:23">
-      <c r="A36" s="19">
+      <c r="A36" s="20">
         <v>32</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="20" t="s">
         <v>74</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2471,21 +2481,21 @@
       </c>
     </row>
     <row r="37" spans="1:23">
-      <c r="A37" s="21">
+      <c r="A37" s="22">
         <v>33</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:23">
-      <c r="A38" s="23">
+      <c r="A38" s="24">
         <v>34</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="24" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -2499,74 +2509,74 @@
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="21">
+      <c r="A39" s="22">
         <v>35</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="25">
         <f>ROUND(L35/(E35*H38/100/H35),0)</f>
         <v>2240</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="J39" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="K39" s="25" t="s">
+      <c r="K39" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="L39" s="25">
+      <c r="L39" s="26">
         <v>0.25</v>
       </c>
-      <c r="M39" s="8" t="s">
+      <c r="M39" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="N39" s="8">
+      <c r="N39" s="9">
         <f>ROUND(P39*(1+2*L39),0)</f>
         <v>3360</v>
       </c>
-      <c r="O39" s="8">
+      <c r="O39" s="9">
         <f>ROUND(P39*(1+1*L39),0)</f>
         <v>2800</v>
       </c>
-      <c r="P39" s="8">
+      <c r="P39" s="9">
         <f>H39</f>
         <v>2240</v>
       </c>
-      <c r="Q39" s="8">
+      <c r="Q39" s="9">
         <f>ROUND(P39*(1-1*L39),0)</f>
         <v>1680</v>
       </c>
-      <c r="R39" s="8">
+      <c r="R39" s="9">
         <f>ROUND(P39*(1-2*L39),0)</f>
         <v>1120</v>
       </c>
-      <c r="S39" s="8" t="str">
+      <c r="S39" s="9" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,N39,1000)</f>
         <v>3360_1000</v>
       </c>
-      <c r="T39" s="8" t="str">
+      <c r="T39" s="9" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,O39,1000)</f>
         <v>2800_1000</v>
       </c>
-      <c r="U39" s="8" t="str">
+      <c r="U39" s="9" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,P39,1000)</f>
         <v>2240_1000</v>
       </c>
-      <c r="V39" s="8" t="str">
+      <c r="V39" s="9" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,Q39,1000)</f>
         <v>1680_1000</v>
       </c>
-      <c r="W39" s="8" t="str">
+      <c r="W39" s="9" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,R39,1000)</f>
         <v>1120_1000</v>
       </c>
@@ -2578,7 +2588,7 @@
       <c r="B40" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="27">
         <v>88</v>
       </c>
     </row>
@@ -2589,7 +2599,7 @@
       <c r="B41" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="27">
         <v>600</v>
       </c>
     </row>
@@ -2600,7 +2610,7 @@
       <c r="B42" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="27">
         <v>18000</v>
       </c>
     </row>
@@ -2611,7 +2621,7 @@
       <c r="B43" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="27">
         <v>1</v>
       </c>
     </row>
@@ -2622,7 +2632,7 @@
       <c r="B44" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="27">
         <v>10</v>
       </c>
     </row>
@@ -2633,7 +2643,7 @@
       <c r="B45" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="27" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2644,7 +2654,7 @@
       <c r="B46" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="28" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2707,16 +2717,16 @@
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="8">
+      <c r="A50" s="9">
         <v>50</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="C50" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="I50" s="8">
+      <c r="I50" s="9">
         <v>600</v>
       </c>
     </row>
@@ -2727,7 +2737,7 @@
       <c r="B51" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="30" t="s">
         <v>108</v>
       </c>
       <c r="I51" s="2">
@@ -2741,7 +2751,7 @@
       <c r="B52" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="30">
+      <c r="D52" s="31">
         <v>30000</v>
       </c>
     </row>
@@ -2752,7 +2762,7 @@
       <c r="B53" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>30000</v>
       </c>
     </row>
@@ -2768,14 +2778,14 @@
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:9">
-      <c r="A55" s="8">
+      <c r="A55" s="9">
         <v>55</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8">
+      <c r="C55" s="9"/>
+      <c r="D55" s="9">
         <v>60</v>
       </c>
     </row>
@@ -2797,18 +2807,18 @@
       <c r="B57" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="32" t="s">
+      <c r="C57" s="33" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="8">
+      <c r="A58" s="9">
         <v>61</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="33" t="s">
+      <c r="C58" s="34" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2819,7 +2829,7 @@
       <c r="B59" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="31" t="s">
+      <c r="C59" s="32" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2841,7 +2851,7 @@
       <c r="B61" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" s="35" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2852,7 +2862,7 @@
       <c r="B62" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" s="35" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2863,10 +2873,10 @@
       <c r="B63" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="35" t="s">
+      <c r="C63" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="35"/>
+      <c r="D63" s="36"/>
     </row>
     <row r="64" s="7" customFormat="1" spans="1:9">
       <c r="A64" s="7">
@@ -2875,8 +2885,8 @@
       <c r="B64" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35">
+      <c r="C64" s="36"/>
+      <c r="D64" s="36">
         <v>5000</v>
       </c>
     </row>
@@ -2887,37 +2897,37 @@
       <c r="B65" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="35" t="s">
+      <c r="C65" s="36" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="36">
+      <c r="A66" s="37">
         <v>80</v>
       </c>
-      <c r="B66" s="36" t="s">
+      <c r="B66" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36">
+      <c r="C66" s="37"/>
+      <c r="D66" s="37">
         <v>259200</v>
       </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="11"/>
-      <c r="Q66" s="11"/>
-      <c r="R66" s="11"/>
-      <c r="S66" s="11"/>
-      <c r="T66" s="11"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
+      <c r="P66" s="12"/>
+      <c r="Q66" s="12"/>
+      <c r="R66" s="12"/>
+      <c r="S66" s="12"/>
+      <c r="T66" s="12"/>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:20">
       <c r="A67" s="1">
@@ -2931,35 +2941,35 @@
       </c>
     </row>
     <row r="68" spans="1:20">
-      <c r="A68" s="8">
+      <c r="A68" s="9">
         <v>100</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:20">
-      <c r="A69" s="8">
+      <c r="A69" s="9">
         <v>101</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:20">
-      <c r="A70" s="8">
+      <c r="A70" s="9">
         <v>102</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D70" s="37">
+      <c r="D70" s="38">
         <v>1022503</v>
       </c>
     </row>
@@ -2970,258 +2980,272 @@
       <c r="B71" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D71" s="26">
+      <c r="D71" s="27">
         <v>4200</v>
       </c>
     </row>
     <row r="72" spans="1:20">
-      <c r="A72" s="8">
+      <c r="A72" s="9">
         <v>111</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="9">
         <v>500</v>
       </c>
     </row>
     <row r="73" spans="1:20">
-      <c r="A73" s="8">
+      <c r="A73" s="9">
         <v>112</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="9">
         <v>300000</v>
       </c>
     </row>
     <row r="74" spans="1:20">
-      <c r="A74" s="8">
+      <c r="A74" s="9">
         <v>113</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:20">
-      <c r="A75" s="8">
+      <c r="A75" s="9">
         <v>114</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="9">
         <v>168</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:20">
-      <c r="A76" s="8">
+      <c r="A76" s="9">
         <v>120</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8">
+      <c r="C76" s="9"/>
+      <c r="D76" s="9">
         <v>5</v>
       </c>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
-      <c r="N76" s="8"/>
-      <c r="O76" s="8"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
+      <c r="L76" s="9"/>
+      <c r="M76" s="9"/>
+      <c r="N76" s="9"/>
+      <c r="O76" s="9"/>
+      <c r="P76" s="9"/>
+      <c r="Q76" s="9"/>
+      <c r="R76" s="9"/>
     </row>
     <row r="77" customFormat="1" spans="1:20">
-      <c r="A77" s="8">
+      <c r="A77" s="9">
         <v>121</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8">
+      <c r="C77" s="9"/>
+      <c r="D77" s="9">
         <v>-1</v>
       </c>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
-      <c r="N77" s="8"/>
-      <c r="O77" s="8"/>
-      <c r="P77" s="8"/>
-      <c r="Q77" s="8"/>
-      <c r="R77" s="8"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+      <c r="O77" s="9"/>
+      <c r="P77" s="9"/>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
     </row>
     <row r="78" customFormat="1" spans="1:20">
-      <c r="A78" s="8">
+      <c r="A78" s="9">
         <v>122</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8">
+      <c r="C78" s="9"/>
+      <c r="D78" s="9">
         <v>99</v>
       </c>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
-      <c r="N78" s="8"/>
-      <c r="O78" s="8"/>
-      <c r="P78" s="8"/>
-      <c r="Q78" s="8"/>
-      <c r="R78" s="8"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="9"/>
+      <c r="N78" s="9"/>
+      <c r="O78" s="9"/>
+      <c r="P78" s="9"/>
+      <c r="Q78" s="9"/>
+      <c r="R78" s="9"/>
     </row>
     <row r="79" customFormat="1" spans="1:20">
-      <c r="A79" s="8">
+      <c r="A79" s="9">
         <v>123</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8">
+      <c r="C79" s="9"/>
+      <c r="D79" s="9">
         <v>30000</v>
       </c>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
-      <c r="N79" s="8"/>
-      <c r="O79" s="8"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="8"/>
-      <c r="R79" s="8"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
+      <c r="M79" s="9"/>
+      <c r="N79" s="9"/>
+      <c r="O79" s="9"/>
+      <c r="P79" s="9"/>
+      <c r="Q79" s="9"/>
+      <c r="R79" s="9"/>
     </row>
     <row r="80" spans="1:20">
-      <c r="A80" s="8">
+      <c r="A80" s="9">
         <v>124</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="8">
+    <row r="81" spans="1:7">
+      <c r="A81" s="9">
         <v>125</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="9" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="8">
+    <row r="82" spans="1:7">
+      <c r="A82" s="9">
         <v>126</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="9">
         <v>20000</v>
       </c>
-      <c r="F82" s="8" t="b">
+      <c r="F82" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83" s="8">
+    <row r="83" spans="1:7">
+      <c r="A83" s="9">
         <v>127</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="8">
+    <row r="84" spans="1:7">
+      <c r="A84" s="9">
         <v>128</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="8">
+    <row r="85" spans="1:7">
+      <c r="A85" s="9">
         <v>129</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="9">
         <v>100000</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="8">
+    <row r="86" spans="1:7">
+      <c r="A86" s="9">
         <v>130</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="9">
         <v>72</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
-      <c r="A87" s="8">
+    <row r="87" spans="1:7">
+      <c r="A87" s="9">
         <v>131</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
-      <c r="A88" s="8">
+    <row r="88" spans="1:7">
+      <c r="A88" s="9">
         <v>135</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="9">
         <v>2</v>
+      </c>
+    </row>
+    <row r="89" s="8" customFormat="1" spans="1:7">
+      <c r="A89" s="8">
+        <v>270</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="213">
   <si>
     <t>sid</t>
   </si>
@@ -999,6 +999,9 @@
   </si>
   <si>
     <t>游戏id,复活所需要的钻石_数量|赠送的金币_数量</t>
+  </si>
+  <si>
+    <t>赛季：免费游戏次数（进阶赛季、循环赛季）</t>
   </si>
 </sst>
 </file>
@@ -2112,7 +2115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W127"/>
+  <dimension ref="A1:W128"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3848,6 +3851,17 @@
         <v>211</v>
       </c>
     </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="8">
+        <v>280</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D128" s="8">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="216">
   <si>
     <t>sid</t>
   </si>
@@ -1002,6 +1002,15 @@
   </si>
   <si>
     <t>赛季：免费游戏次数（进阶赛季、循环赛季）</t>
+  </si>
+  <si>
+    <t>赛季：进阶赛季、循环赛季，在玩slot游戏过程中，触发被动匹配的概率（百分比）</t>
+  </si>
+  <si>
+    <t>赛季：进阶赛季，竞技匹配成功后，根据多少局的游戏总结果来判定输赢</t>
+  </si>
+  <si>
+    <t>赛季：循环赛季，竞技匹配成功后，根据多少局的游戏总结果来判定输赢</t>
   </si>
 </sst>
 </file>
@@ -2115,7 +2124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W128"/>
+  <dimension ref="A1:W131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3862,6 +3871,39 @@
         <v>10</v>
       </c>
     </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="8">
+        <v>281</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D129" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="8">
+        <v>282</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D130" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="8">
+        <v>283</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D131" s="8">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="218">
   <si>
     <t>sid</t>
   </si>
@@ -1011,6 +1011,12 @@
   </si>
   <si>
     <t>赛季：循环赛季，竞技匹配成功后，根据多少局的游戏总结果来判定输赢</t>
+  </si>
+  <si>
+    <t>通行证：初级付费通行证解锁金额</t>
+  </si>
+  <si>
+    <t>通行证：高级付费通行证解锁金额</t>
   </si>
 </sst>
 </file>
@@ -2124,7 +2130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W131"/>
+  <dimension ref="A1:W133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3904,6 +3910,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="8">
+        <v>290</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D132" s="8">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="8">
+        <v>291</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D133" s="8">
+        <v>99.99</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="220">
   <si>
     <t>sid</t>
   </si>
@@ -683,7 +683,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_214300</t>
+    <t>1990000_8880000</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
@@ -1011,6 +1011,12 @@
   </si>
   <si>
     <t>赛季：循环赛季，竞技匹配成功后，根据多少局的游戏总结果来判定输赢</t>
+  </si>
+  <si>
+    <t>赛季：赛季结算，赛季币返还的比例与上限</t>
+  </si>
+  <si>
+    <t>30_2000</t>
   </si>
   <si>
     <t>通行证：初级付费通行证解锁金额</t>
@@ -2130,7 +2136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W133"/>
+  <dimension ref="A1:W134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3912,23 +3918,34 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="8">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B132" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="D132" s="8">
-        <v>29.99</v>
+      <c r="C132" s="8" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="8">
+        <v>290</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D133" s="8">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="8">
         <v>291</v>
       </c>
-      <c r="B133" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D133" s="8">
+      <c r="B134" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D134" s="8">
         <v>99.99</v>
       </c>
     </row>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -683,7 +683,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_8880000</t>
+    <t>1990000_8880000|1024001_10|1024007_10</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
@@ -719,7 +719,7 @@
     <t>隐私政策链接</t>
   </si>
   <si>
-    <t>https://lls.cdjjgkj.cn/privacy-policy.html</t>
+    <t>https://manage.gametycoon.top/privacy-policy.html</t>
   </si>
   <si>
     <t>推广分享：分享1人得固定奖励</t>
@@ -989,7 +989,7 @@
     <t>用户协议：链接配置</t>
   </si>
   <si>
-    <t>https://lls.cdjjgkj.cn/terms-of-service.html</t>
+    <t>https://manage.gametycoon.top/terms-of-service.html</t>
   </si>
   <si>
     <t>斗仙牌复活游戏所需钻石金额以及复活后赠送金币金额</t>
@@ -3854,7 +3854,7 @@
       <c r="B126" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3952,7 +3952,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
-    <hyperlink ref="C58" r:id="rId4" display="https://lls.cdjjgkj.cn/privacy-policy.html"/>
+    <hyperlink ref="C58" r:id="rId4" display="https://manage.gametycoon.top/privacy-policy.html" tooltip="https://manage.gametycoon.top/privacy-policy.html"/>
+    <hyperlink ref="C126" r:id="rId5" display="https://manage.gametycoon.top/terms-of-service.html" tooltip="https://manage.gametycoon.top/terms-of-service.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -683,7 +683,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_8880000|1024001_10|1024007_10</t>
+    <t>1990000_880000|1024001_10|1024007_10</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -1244,12 +1244,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3800,7 +3800,7 @@
         <v>202</v>
       </c>
       <c r="D121" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:7">

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -1244,12 +1244,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3844,7 +3844,7 @@
         <v>206</v>
       </c>
       <c r="D125" s="8">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:7">

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8">
-        <v>5</v>
+        <v>9999</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="221">
   <si>
     <t>sid</t>
   </si>
@@ -1023,6 +1023,9 @@
   </si>
   <si>
     <t>通行证：高级付费通行证解锁金额</t>
+  </si>
+  <si>
+    <t>游客：从游戏返回模拟经营场景，场景中的游客小人数量参数</t>
   </si>
 </sst>
 </file>
@@ -2136,7 +2139,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W134"/>
+  <dimension ref="A1:W135"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3949,6 +3952,17 @@
         <v>99.99</v>
       </c>
     </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="8">
+        <v>292</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D135" s="8">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8">
-        <v>9999</v>
+        <v>999999</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -683,7 +688,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_880000|1024001_10|1024007_10</t>
+    <t>1990000_888000|1024001_20|1024007_20|1024014_20|1024008_100|1024013_10|1125402_100</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -688,7 +688,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_888000|1024001_20|1024007_20|1024014_20|1024008_100|1024013_10|1125402_100</t>
+    <t>1990000_888000|1024001_2000|1024007_20|1024014_20|1024008_100|1024013_10|1125402_100</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="223">
   <si>
     <t>sid</t>
   </si>
@@ -1031,6 +1031,12 @@
   </si>
   <si>
     <t>游客：从游戏返回模拟经营场景，场景中的游客小人数量参数</t>
+  </si>
+  <si>
+    <t>生成游客的前提条件：完成指定的引导ID(范围，任何一个ID被完成 即可触发生成游客的功能)</t>
+  </si>
+  <si>
+    <t>1012_1013_1014</t>
   </si>
 </sst>
 </file>
@@ -2144,7 +2150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W135"/>
+  <dimension ref="A1:W136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3968,6 +3974,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="8">
+        <v>300</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -1000,7 +1000,7 @@
     <t>斗仙牌复活游戏所需钻石金额以及复活后赠送金币金额</t>
   </si>
   <si>
-    <t>300800,1980000_20|1990000_10000</t>
+    <t>300800,1980000_20|1960000_10000</t>
   </si>
   <si>
     <t>游戏id,复活所需要的钻石_数量|赠送的金币_数量</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="224">
   <si>
     <t>sid</t>
   </si>
@@ -853,13 +853,16 @@
     <t>广告：奖励收益倍数(必随机一个倍数)</t>
   </si>
   <si>
-    <t>1.5_2000|2_2000|3_3000</t>
+    <t>2_2000|2_2000|2_2000</t>
   </si>
   <si>
     <t>广告：看一次广告清除的时间(分)</t>
   </si>
   <si>
     <t>广告：建筑每次升级看广告次数</t>
+  </si>
+  <si>
+    <t>清建筑CD：X钻石清一分钟CD时间</t>
   </si>
   <si>
     <t>游客在赌场中设备的交互时间（秒）</t>
@@ -2150,7 +2153,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W136"/>
+  <dimension ref="A1:W137"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3467,132 +3470,131 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="8">
-        <v>200</v>
+        <v>138</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>164</v>
       </c>
       <c r="D91" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="8">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>166</v>
+      <c r="D92" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="8">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B93" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="8">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>169</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="8">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B95" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>170</v>
-      </c>
-      <c r="D95" s="8">
-        <v>1024007</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>171</v>
       </c>
       <c r="D96" s="8">
-        <v>2</v>
+        <v>1024007</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="8">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C97" s="38" t="s">
-        <v>173</v>
+      <c r="D97" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="8">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B98" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C98" s="38" t="s">
         <v>174</v>
-      </c>
-      <c r="C98" s="38"/>
-      <c r="D98" s="8">
-        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="8">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>175</v>
       </c>
       <c r="C99" s="38"/>
       <c r="D99" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="8">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>176</v>
       </c>
       <c r="C100" s="38"/>
       <c r="D100" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>177</v>
       </c>
       <c r="C101" s="38"/>
       <c r="D101" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="8">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>178</v>
@@ -3604,7 +3606,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="8">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>179</v>
@@ -3616,53 +3618,54 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="8">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>180</v>
       </c>
       <c r="C104" s="38"/>
       <c r="D104" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="8">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C105" s="39" t="s">
-        <v>182</v>
+      <c r="C105" s="38"/>
+      <c r="D105" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="8">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B106" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C106" s="39" t="s">
         <v>183</v>
-      </c>
-      <c r="C106" s="38"/>
-      <c r="D106" s="8">
-        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="8">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>184</v>
       </c>
+      <c r="C107" s="38"/>
       <c r="D107" s="8">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="8">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>185</v>
@@ -3673,51 +3676,51 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="8">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B109" s="8" t="s">
         <v>186</v>
       </c>
       <c r="D109" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="8">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D110" s="8">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="8">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B111" s="8" t="s">
         <v>188</v>
       </c>
       <c r="D111" s="8">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="8">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B112" s="8" t="s">
         <v>189</v>
       </c>
       <c r="D112" s="8">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>190</v>
@@ -3728,76 +3731,76 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="8">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B114" s="8" t="s">
         <v>191</v>
       </c>
       <c r="D114" s="8">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="8">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B115" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C115" s="38" t="s">
-        <v>193</v>
+      <c r="D115" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B116" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C116" s="38" t="s">
         <v>194</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="8">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B117" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="G117" s="8" t="s">
         <v>197</v>
-      </c>
-      <c r="D117" s="8">
-        <v>50</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="8">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B118" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C118" s="8" t="s">
-        <v>199</v>
+      <c r="D118" s="8">
+        <v>50</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="8">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B119" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C119" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="D119" s="8">
-        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="8">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>201</v>
@@ -3808,188 +3811,199 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="8">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>202</v>
       </c>
       <c r="D121" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="8">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>203</v>
       </c>
       <c r="D122" s="8">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="8">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>204</v>
       </c>
       <c r="D123" s="8">
-        <v>20000</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="8">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B124" s="8" t="s">
         <v>205</v>
       </c>
       <c r="D124" s="8">
-        <v>5</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="8">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B125" s="8" t="s">
         <v>206</v>
       </c>
       <c r="D125" s="8">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="8">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C126" t="s">
-        <v>208</v>
+      <c r="D126" s="8">
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="8">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B127" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C127" t="s">
         <v>209</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="8">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B128" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="G128" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="D128" s="8">
-        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="8">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B129" s="8" t="s">
         <v>213</v>
       </c>
       <c r="D129" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="8">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B130" s="8" t="s">
         <v>214</v>
       </c>
       <c r="D130" s="8">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="8">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B131" s="8" t="s">
         <v>215</v>
       </c>
       <c r="D131" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="8">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B132" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C132" s="8" t="s">
-        <v>217</v>
+      <c r="D132" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="8">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B133" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C133" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="D133" s="8">
-        <v>29.99</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="8">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B134" s="8" t="s">
         <v>219</v>
       </c>
       <c r="D134" s="8">
-        <v>99.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="8">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>220</v>
       </c>
       <c r="D135" s="8">
-        <v>2</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="8">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B136" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="D136" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="8">
+        <v>300</v>
+      </c>
+      <c r="B137" s="8" t="s">
         <v>222</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
     <hyperlink ref="C58" r:id="rId4" display="https://manage.gametycoon.top/privacy-policy.html" tooltip="https://manage.gametycoon.top/privacy-policy.html"/>
-    <hyperlink ref="C126" r:id="rId5" display="https://manage.gametycoon.top/terms-of-service.html" tooltip="https://manage.gametycoon.top/terms-of-service.html"/>
+    <hyperlink ref="C127" r:id="rId5" display="https://manage.gametycoon.top/terms-of-service.html" tooltip="https://manage.gametycoon.top/terms-of-service.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -688,7 +688,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_888000|1024001_2000|1024007_20|1024014_20|1024008_100|1024013_10|1125402_100</t>
+    <t>1990000_288000</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="226">
   <si>
     <t>sid</t>
   </si>
@@ -1040,6 +1040,12 @@
   </si>
   <si>
     <t>1012_1013_1014</t>
+  </si>
+  <si>
+    <t>游客（品质刷新）：知名度预期上限值</t>
+  </si>
+  <si>
+    <t>雇员：所有加成的属性值预期上限值</t>
   </si>
 </sst>
 </file>
@@ -2153,7 +2159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W137"/>
+  <dimension ref="A1:W139"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3999,6 +4005,28 @@
         <v>223</v>
       </c>
     </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="8">
+        <v>301</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D138" s="8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="8">
+        <v>302</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D139" s="8">
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="233">
   <si>
     <t>sid</t>
   </si>
@@ -1046,6 +1046,27 @@
   </si>
   <si>
     <t>雇员：所有加成的属性值预期上限值</t>
+  </si>
+  <si>
+    <t>快速获取资源：每日快速获取资源（观看视频）的次数上限</t>
+  </si>
+  <si>
+    <t>快速获取资源：每日观看视频可以快速获取累计了多长时间的资源（单位：h）</t>
+  </si>
+  <si>
+    <t>快速获取资源：每日观看视频的观看CD是多长时间（单位：min）</t>
+  </si>
+  <si>
+    <t>快速获取资源：每日快速获取资源（花费钻石）的次数上限</t>
+  </si>
+  <si>
+    <t>快速获取资源：每日花费钻石可以快速获取累计了多长时间的资源（单位：h）</t>
+  </si>
+  <si>
+    <t>快速获取资源：每次快速获取资源需要花费的钻石数量</t>
+  </si>
+  <si>
+    <t>198000_100,200,400</t>
   </si>
 </sst>
 </file>
@@ -2159,7 +2180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W139"/>
+  <dimension ref="A1:W145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -4027,6 +4048,72 @@
         <v>30000</v>
       </c>
     </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="8">
+        <v>303</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D140" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="8">
+        <v>304</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D141" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="8">
+        <v>305</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D142" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="8">
+        <v>306</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D143" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="8">
+        <v>307</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D144" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="8">
+        <v>308</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -1063,10 +1063,10 @@
     <t>快速获取资源：每日花费钻石可以快速获取累计了多长时间的资源（单位：h）</t>
   </si>
   <si>
-    <t>快速获取资源：每次快速获取资源需要花费的钻石数量</t>
-  </si>
-  <si>
-    <t>198000_100,200,400</t>
+    <t>快速获取资源：每次快速获取资源需要花费的道具与数量</t>
+  </si>
+  <si>
+    <t>1980000_100,200,400</t>
   </si>
 </sst>
 </file>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="235">
   <si>
     <t>sid</t>
   </si>
@@ -1067,6 +1067,12 @@
   </si>
   <si>
     <t>1980000_100,200,400</t>
+  </si>
+  <si>
+    <t>挖矿小游戏：多长时间恢复（获得）一个道具镐（单位：分钟）与回复的上限</t>
+  </si>
+  <si>
+    <t>10_400</t>
   </si>
 </sst>
 </file>
@@ -2180,7 +2186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W145"/>
+  <dimension ref="A1:W146"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3989,7 +3995,7 @@
       <c r="B134" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D134" s="8">
+      <c r="C134" s="8">
         <v>29.99</v>
       </c>
     </row>
@@ -4000,7 +4006,7 @@
       <c r="B135" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="D135" s="8">
+      <c r="C135" s="8">
         <v>99.99</v>
       </c>
     </row>
@@ -4112,6 +4118,17 @@
       </c>
       <c r="C145" s="8" t="s">
         <v>232</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="8">
+        <v>320</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="239">
   <si>
     <t>sid</t>
   </si>
@@ -1073,6 +1073,18 @@
   </si>
   <si>
     <t>10_400</t>
+  </si>
+  <si>
+    <t>数据中心：当前容纳人数 高于 总容纳人数的【N%】 爆红</t>
+  </si>
+  <si>
+    <t>数据中心：当前容纳人数 低于 总容纳人数的 【N%】 打标签“收益过低”</t>
+  </si>
+  <si>
+    <t>数据中心：当前每分钟获客人数 低于 每分钟标准获客人数的 【N%】打标签“收益过低”</t>
+  </si>
+  <si>
+    <t>数据中心：当前满意度 低于 标准满意度的 【N%】 打标签 “收益过低”</t>
   </si>
 </sst>
 </file>
@@ -2186,7 +2198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W146"/>
+  <dimension ref="A1:W150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -4109,7 +4121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:4">
       <c r="A145" s="8">
         <v>308</v>
       </c>
@@ -4120,7 +4132,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:4">
       <c r="A146" s="8">
         <v>320</v>
       </c>
@@ -4129,6 +4141,50 @@
       </c>
       <c r="C146" s="8" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="8">
+        <v>331</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D147" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="8">
+        <v>332</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D148" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="8">
+        <v>333</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D149" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="8">
+        <v>334</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D150" s="8">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -4052,7 +4052,7 @@
         <v>224</v>
       </c>
       <c r="D138" s="8">
-        <v>10000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="139" spans="1:4">

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="245">
   <si>
     <t>sid</t>
   </si>
@@ -1067,6 +1067,24 @@
   </si>
   <si>
     <t>1980000_100,200,400</t>
+  </si>
+  <si>
+    <t>指定生成游客：每日的刷新时间点</t>
+  </si>
+  <si>
+    <t>0_6_10_14_19</t>
+  </si>
+  <si>
+    <t>指定生成游客：每次手动刷新所需要的费用</t>
+  </si>
+  <si>
+    <t>1980000_20|1980000_30|1980000_40|1980000_50|1980000_50</t>
+  </si>
+  <si>
+    <t>指定生成游客：每个时间段手动刷新的次数上限</t>
+  </si>
+  <si>
+    <t>指定生成游客：每次刷新出现的游客购买次数上限</t>
   </si>
   <si>
     <t>挖矿小游戏：多长时间恢复（获得）一个道具镐（单位：分钟）与回复的上限</t>
@@ -2198,7 +2216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W150"/>
+  <dimension ref="A1:W154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -4134,7 +4152,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="8">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B146" s="8" t="s">
         <v>233</v>
@@ -4145,45 +4163,89 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="8">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="B147" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D147" s="8">
-        <v>80</v>
+      <c r="C147" s="8" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="8">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D148" s="8">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="8">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D149" s="8">
-        <v>80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="8">
+        <v>320</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="8">
+        <v>331</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D151" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="8">
+        <v>332</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D152" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="8">
+        <v>333</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D153" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="8">
         <v>334</v>
       </c>
-      <c r="B150" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D150" s="8">
+      <c r="B154" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D154" s="8">
         <v>80</v>
       </c>
     </row>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -688,7 +688,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_288000</t>
+    <t>1990000_12000</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
@@ -4136,7 +4136,7 @@
         <v>230</v>
       </c>
       <c r="D144" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145" spans="1:4">

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>

--- a/poker/resources/sample/global.xlsx
+++ b/poker/resources/sample/global.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="250">
   <si>
     <t>sid</t>
   </si>
@@ -688,7 +688,7 @@
     <t>新手奖励</t>
   </si>
   <si>
-    <t>1990000_12000</t>
+    <t>1990000_18000</t>
   </si>
   <si>
     <t>手机短信区号（印度、巴基斯坦、菲律宾、巴西、尼日利亚）废弃</t>
@@ -1103,6 +1103,21 @@
   </si>
   <si>
     <t>数据中心：当前满意度 低于 标准满意度的 【N%】 打标签 “收益过低”</t>
+  </si>
+  <si>
+    <t>活跃通行证：每期通行证购买的等级积分上限</t>
+  </si>
+  <si>
+    <t>活跃通行证：购买通行证等级积分的价格（道具ID_数量_积分数量）</t>
+  </si>
+  <si>
+    <t>1980000_100_10</t>
+  </si>
+  <si>
+    <t>活跃通行证：通行证图标可以在哪些游戏界面中显示（填写游戏ID）</t>
+  </si>
+  <si>
+    <t>103900_102700_100700_101800_103100_102500_101200_100300_101500_102000_102100_102200</t>
   </si>
 </sst>
 </file>
@@ -1828,7 +1843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1891,6 +1906,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2216,7 +2232,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W154"/>
+  <dimension ref="A1:W157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -2385,7 +2401,7 @@
       <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="41" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="15"/>
@@ -2402,7 +2418,7 @@
       <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="42" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="12"/>
@@ -2419,7 +2435,7 @@
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="42" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="12"/>
@@ -2436,7 +2452,7 @@
       <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="42" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="12"/>
@@ -2453,7 +2469,7 @@
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="42" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="12"/>
@@ -4249,6 +4265,42 @@
         <v>80</v>
       </c>
     </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="40">
+        <v>350</v>
+      </c>
+      <c r="B155" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C155" s="40"/>
+      <c r="D155" s="40">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="40">
+        <v>351</v>
+      </c>
+      <c r="B156" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C156" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D156" s="40"/>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="40">
+        <v>352</v>
+      </c>
+      <c r="B157" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="C157" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="D157" s="40"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C57" r:id="rId3" display="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png" tooltip="https://aws-s3-jjg-asset-bucket.s3.ap-southeast-1.amazonaws.com/tanchuang_res/english/tc_sc_1.png"/>
